--- a/saida/produtos_enriquecidos_parte_3.xlsx
+++ b/saida/produtos_enriquecidos_parte_3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1269,20 +1269,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Marca: Guepar Bond, Modelo: 977, Conteúdo: 20g, Tipo: Adesivo instantâneo, Cor: Transparente, Secagem: Rápida (alguns segundos)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.mercadolivre.com.br/cola-adesivo-instantaneo-977-20g-guepar-bond-kit-com-5und/up/MLBU3698447886</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>https://datasheets.tdx.henkel.com/LOCTITE-Super-Bonder-Original-pt_BR.pdf</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://acdn-us.mitiendanube.com/stores/002/702/853/products/2-a3b0163e18a5f1869517467092352457-1024-1024.webp | https://http2.mlstatic.com/D_Q_NP_2X_708211-MLA103758261857_012026-P.webp</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1605,12 +1609,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Aparência: Pasta Lisa Sem Partículas, Cores: Branco, Incolor, Preto, Criação de Película (minutos): 7, Tempo de Cura Total (3mm/hora): 24 Horas, Relação Máxima de Alongamento %: 200, Dureza Shore A (curado): 50 ~ 60, Temperatura de Serviço °C: -40° A + 90°</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.silvaselantes.com.br/935-estrutural.html</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1618,7 +1622,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.silvaselantes.com.br/media/catalog/product/cache/1/image/600x600/9df78eab33525d08d6e5fb8d27136e95/e/s/estr.webp | https://www.silvaselantes.com.br/media/catalog/product/cache/1/image/600x600/9df78eab33525d08d6e5fb8d27136e95/s/e/selante_estutural_site.webp</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1653,20 +1661,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Resistência à compressão: 50 MPa (1 dia), 70 MPa (7 dias); Densidade: 1,70 kg/l; Consistência: Fluído; Cor: Cinza; Embalagem: Caixa com 6 conjuntos de 1kg (A + B); Prazo de validade: 24 meses a partir da data de produção.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://bra.sika.com/dam/dms/br01/i/sikadur-epoxi.pdf</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>https://bra.sika.com/dam/dms/br01/i/sikadur-epoxi.pdf</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://impermarket.vtexassets.com/arquivos/ids/637076-800-auto?v=639257425245970000&amp;width=800&amp;height=auto&amp;aspect=true | https://impermarket.vtexassets.com/arquivos/ids/611803-800-auto?v=639035014975070000&amp;width=800&amp;height=auto&amp;aspect=true</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1749,20 +1761,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Aparência: Pasta translúcida com odor característico (ácido acético). Densidade a 25 ºC: 0,93 à 1,05 g/mL. Tempo de formação de película: ≤ 20 minutos. Temperatura ideal de aplicação: + 5 à 45°C. Temperatura de trabalho: - 50 à 150°C. Alongamento à ruptura: ≥ 500 %. Dureza Shore A: 25. Cura gradativa a 23°C e 55% U.R. após 24 horas: ≥3 mm. Tempo de armazenamento a 20°C: 12 meses.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://construja.com.br/produto/136200/pulvitec-silicone-acetico-250g-branco</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>https://www.tekbond.com.br/sites/Tekbond.com.br/files/media-library/product/BRSA004/documents/technical_sheet/downloadable_file/Silicone_Acetico_Construcao-BRSA004-ficha_tecnica_01.pdf</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://santil.jetassets.com.br/produto/SILICONE-ACETICO-50G-BRANCO-22004001202_D.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1797,20 +1813,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Aparência: Pasta translúcida com odor característico (ácido acético); Densidade a 25 ºC: 0,93 à 1,05 g/mL; Tempo de formação de película: ≤ 20 minutos; Temperatura ideal de aplicação: + 5 à 45°C; Temperatura de trabalho: - 50 à 150°C; Alongamento à ruptura: ≥ 500 %; Dureza Shore A: 25; Cura gradativa a 23°C e 55% U.R. após 24 horas: ≥3 mm; Tempo de armazenamento a 20°C: 12 meses.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.tekbond.com.br/sites/Tekbond.com.br/files/media-library/product/BRSA004/documents/technical_sheet/downloadable_file/Silicone_Acetico_Construcao-BRSA004-ficha_tecnica_01.pdf</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>https://www.tekbond.com.br/sites/Tekbond.com.br/files/media-library/product/BRSA004/documents/technical_sheet/downloadable_file/Silicone_Acetico_Construcao-BRSA004-ficha_tecnica_01.pdf</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://cdn.dooca.store/1138/products/adesivo-de-silicone-acetico-incolor-280g-c-06un_640x640+fill_ffffff.png?v=1696888228 | https://images.cws.digital/produtos/p/52/20/silicone-acetico-incolor-250g-leo-10282052-1718032558195.jpg | https://images.cws.digital/produtos/p/52/20/silicone-acetico-incolor-250g-leo-10282052-1718032555631.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1845,20 +1865,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Aparência: Pasta translúcida com odor característico (ácido acético); Densidade: 0,93 à 1,05 g/mL; Tempo de formação de película: ≤ 20 minutos; Temperatura ideal de aplicação: +5 à 45°C; Temperatura de trabalho: -50 à 150°C; Alongamento à ruptura: ≥ 500%; Dureza Shore A: 25; Cura gradativa após 24 horas: ≥3 mm; Tempo de armazenamento: 12 meses.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.amazon.com.br/Adesivo-Silicone-Ac%C3%A9tico-Preto-Tekbond/dp/B0D8TYW25H</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>https://www.tekbond.com.br/sites/Tekbond.com.br/files/media-library/product/BRSA004/documents/technical_sheet/downloadable_file/Silicone_Acetico_Construcao-BRSA004-ficha_tecnica_01.pdf</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41Hu43gHpnL._SX38_SY50_CR,0,0,38,50_.jpg | https://m.media-amazon.com/images/I/415JSB-BoRL._SX38_S</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2126,16 +2150,8 @@
           <t>COLA / ADESIVO</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -2227,11 +2243,7 @@
           <t>Silicone PU Aluzinco Cinza, um produto da marca Silva.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -2467,11 +2479,7 @@
           <t>SILICONE PU FLEX 40 CINZA, um produto da marca SILVA.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -2517,20 +2525,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Temperatura de aplicação: -20°C, disponível nas cores branco, preto e cinza, em tubos e sachês. Curas ao entrar em contato com a umidade ambiente, formando um elastômero de alta resistência.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.mercadolivre.com.br/pu-flex-40-preto-silva-selantes-adesivo-hibrido-pu-40/up/MLBU5118267765</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>https://alphaville-rj.com.br/wp-content/uploads/2024/07/Catalogo-Digital-2024-Silva-Selantes-Alphaville-compressed.pdf</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.silvaselantes.com.br/media/catalog/product/cache/1/small_image/200x200/9df78eab33525d08d6e5fb8d27136e95/f/l/flex_1.webp | https://a-static.mlcdn.com.br/450pxx450px/selante-pu-flex-40-preto-silva-selantes/calhaskairos/puflex40preto/ebf429264b34c628b461f96d011a9b03.jpeg | https://www.silvaselantes.com.br/media/catalog/product/cache/1/image/600x600/9df78eab33525d08d6e5fb8d27136e95/4/0/400.png</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2565,20 +2577,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Alta elasticidade, resistência UV, fungicida, aplicável em cerâmicas, vidros e alumínios, composição química inclui Dimetil Siloxano Hidroxiterminado (65-75%), Metil Triacetoxi Silano (2-5%), Etil Triacetoxi Silano (2-5%), Silica amorfa (7-10%).</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.silvaselantes.com.br</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>https://www.silvaselantes.com.br/amfilerating/file/download/file_id/56/</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.silvaselantes.com.br/media/catalog/product/cache/1/small_image/9df78eab33525d08d6e5fb8d27136e95/v/i/vid.alum.1200x600px.webp | https://www.silvaselantes.com.br/media/catalog/product/cache/1/small_image/600x600/9df78eab33525d08d6e5fb8d27136e95/f/i/fix.webp</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2709,12 +2725,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Volume: 300ml / 270g</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://stoky.com.br/produto/40514</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2722,7 +2738,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://portal.zydon.com.br/api/files/01a00074-e6e3-84f0-8a13-23abe0fcfc9f/content?ingress=stoky.com.br | https://i.ytimg.com/vi/8XxjikPaRKA/maxresdefault.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2757,20 +2777,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Tempo de formação de pele: 10 a 20 minutos; Cura total: 72 horas; Teor de sólidos: 60 ± 5%; Densidade: 0,90 ± 0,05 g/cm³; Rendimento: 12 m lineares (filete de 5mm²); Resistência à temperatura: -10 a 80°C; Cor: Cinza.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://dualeshop.com.br/selantevedacalhascinza360g-silvaselantes.html</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>https://tytan-cdn.tytan.com/uploads/sites/5/2020/11/TYTAN-PROFESSIONAL-Adesivo-Veda-Calha_01-02-2024_TDS_pt.pdf</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://dualeshop.com.br/media/catalog/product/cache/b7979decf75865fe9fd06c7f89e3241a/1/_/1_1228.jpg | https://dualeshop.com.br/media/catalog/product/cache/b7979decf75865fe9fd06c7f89e3241a/3/_/3_1143.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2800,25 +2824,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Óleo lubrificante anticorrosivo para proteção de superfícies metálicas, formando um filme oleoso que não seca e protege por longos períodos. Utilizado em compressores de ar a pistão e em peças estocadas.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Ponto de Fulgor: 38°C; Densidade: 0,82 – 0,83 g/cm³; Não Voláteis: 36,0%; Taxa de Evaporação: 12; Resistência Câmara Salina: 72h (ASTM B-117); Corrosividade ao cobre: 1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>http://www.comprasnet.gov.br/ConsultaLicitacoes/download/download_editais_detalhe.asp?coduasg=120072&amp;modprp=5&amp;numprp=662015</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>https://www.allchem.com.br/media/sparsh/product_attachment/FT_-_PROTETIVO_ANTICORROSIVO_557.pdf</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://carrefourbr.vtexassets.com/arquivos/ids/212946556-848-848/image-0.jpg?v=639064164468100000 | https://carrefourbr.vtexassets.com/arquivos/ids/212946558-848-848/image-1.jpg?v=639064164469530000</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2901,7 +2929,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Peso: 100g, Aprovado no FDA sob nº 1789.3570, Faixa de temperatura de trabalho: -51 a +163 °C, Alta capacidade de suportar cargas, Ótima resistência ao desgaste, Maior prazo de relubrificação, Boa compatibilidade com materiais industriais, Excelente torque à baixas temperaturas, Resistente à lavagem com água.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3091,11 +3119,7 @@
           <t>Oleo tipo Singer, utilizado em máquinas de costura para lubrificação.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -3187,11 +3211,7 @@
           <t>Anti respingo com silicone em lata, produto utilizado para evitar respingos de líquidos.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4339,11 +4359,7 @@
           <t>Esmalte epóxi cinza claro N6,5 em embalagem de 2,7 litros, da marca Afetintas.</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4387,11 +4403,7 @@
           <t>Esmalte epóxi preto N1, lata de 2,7 litros, da marca Afetintas.</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4402,7 +4414,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://verginia.vtexassets.com/arquivos/ids/157362/Tinta-Esmalte-Epoxi-Farben-27L.png?v=638380936780500000 | https://bite.vtexassets.com/arquivos/ids/177996/Fleet-Color-27.png.png?v=639208547600400000 | https://www.tintassaojose.com.br/media/catalog/product/cache/1/image/500x/9df78eab33525d08d6e5fb8d27136e95/i/m/image_5624.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4771,11 +4787,7 @@
           <t>Galvanitex Cinza Claro Fosco 0,9, um produto de acabamento para superfícies metálicas.</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4786,7 +4798,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1377675/tinta_galvanitex_cinza_claro_fosco_36l_1_20250715161457_79b7102156a8.jpg | https://images.tcdn.com.br/img/img_prod/1377675/tinta_galvanitex_cinza_claro_fosco_18l_1_20250715161226_971ca2a25a29.jpg | https://tb1131.vtexassets.com/arquivos/ids/275683/2807-GALVANITEXCINZACLAROFOSCO900ML-SOLVENTEX.png?v=639036408184470000</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">

--- a/saida/produtos_enriquecidos_parte_3.xlsx
+++ b/saida/produtos_enriquecidos_parte_3.xlsx
@@ -4835,11 +4835,7 @@
           <t>Galvanitex Cinza Claro Fosco 3,6, um produto de acabamento para superfícies metálicas.</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4931,11 +4927,7 @@
           <t>Galvoprimer Coral é um primário acrílico à base de água, na cor branca, disponível em embalagem de 3,6 litros.</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5267,11 +5259,7 @@
           <t>Tinta Esmalte Coralit Ultra Resistência, um produto de alta durabilidade e resistência para pinturas.</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5315,11 +5303,7 @@
           <t>Tinta spray metálica na cor cobre.</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5363,11 +5347,7 @@
           <t>Tinta spray metálica cromada para aplicação em diversas superfícies.</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5411,11 +5391,7 @@
           <t>Tinta spray metálica dourada para aplicação em diversos materiais.</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5459,11 +5435,7 @@
           <t>Tinta spray de uso geral na cor alumínio, ideal para diversos tipos de superfícies.</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5507,11 +5479,7 @@
           <t>Tinta spray amarela para uso geral.</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5555,11 +5523,7 @@
           <t>Tinta spray de uso geral na cor azul, ideal para pintura rápida e uniforme em diversos materiais.</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5603,11 +5567,7 @@
           <t>Tinta spray de uso geral na cor branca com acabamento brilhante.</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5651,11 +5611,7 @@
           <t>Tinta spray branca fosca para uso geral.</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5699,11 +5655,7 @@
           <t>Tinta spray de uso geral na cor preto brilho.</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5747,11 +5699,7 @@
           <t>Tinta spray de uso geral na cor preto fosco, ideal para pintura de superfícies variadas.</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5795,11 +5743,7 @@
           <t>Tinta spray de uso geral na cor verde.</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -5843,11 +5787,7 @@
           <t>Tinta spray de uso geral na cor vermelha.</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -6179,11 +6119,7 @@
           <t>ZARCAO SOLVENTEX 1/4 551 CINZA, um produto da marca ZARCAO, provavelmente relacionado a materiais de construção ou limpeza.</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -6227,11 +6163,7 @@
           <t>ZARCAO SOLVENTEX 1/4 564 VERDE, um produto químico utilizado para limpeza e remoção de resíduos.</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -6275,11 +6207,7 @@
           <t>ZARCAO SOLVENTEX 1/4 990 VERM, um produto de limpeza ou solvente.</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -6323,11 +6251,7 @@
           <t>O ZARCAO SOLVENTEX 18L 551 CINZA é um produto de pintura ou revestimento em tonalidade cinza, disponível em embalagem de 18 litros.</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -6611,11 +6535,7 @@
           <t>ZARCAO SOLVENTEX 9002 ESPECIAL 1/4, um produto químico utilizado para diversas aplicações industriais.</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -6659,11 +6579,7 @@
           <t>Zarcao Solventex 9002 Especial, um solvente de alta qualidade em embalagem de 18 litros.</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -6755,11 +6671,7 @@
           <t>O ZARCAO SOLVENTEX 969 PRETO 1/4 é um produto, possivelmente uma ferramenta ou material de construção, na cor preta.</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Não encontradas especificações técnicas no contexto fornecido.</t>
-        </is>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8819,11 +8731,7 @@
           <t>Cilindro STAM 803/804/1801 com parafuso, acabamento cromado.</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8867,11 +8775,7 @@
           <t>Macaneta STAM, um produto cujas informações específicas não foram encontradas.</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8963,11 +8867,7 @@
           <t>Dobradica C1001FG 2''. Dobradica de alta qualidade para uso em diversos projetos e aplicações.</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9006,16 +8906,8 @@
           <t>DOBRADICA/PORTA CADEADO</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Dobradica C1001FG 2.1/2''. Produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9971,11 +9863,7 @@
           <t>Dobradica para portão, modelo CHUMB. FOE25.</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10019,11 +9907,7 @@
           <t>Dobradica para portão, modelo FOE 20.</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10446,16 +10330,8 @@
           <t>DOBRADICA/PORTA CADEADO</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Porta cadeado FG de 2 polegadas. Produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10499,11 +10375,7 @@
           <t>Cadeado automático da marca Tetra São Salvador, modelo Ref 301.</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10547,11 +10419,7 @@
           <t>Cadeado automático da marca São Salvador, modelo Ref 901.</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10595,11 +10463,7 @@
           <t>Cadeado mini tetra São Salvador, modelo ref 701, um pequeno cadeado tetra para uso geral.</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10643,11 +10507,7 @@
           <t>Cadeado de porta de aço da marca Dovale, modelo King, cor verde.</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10739,11 +10599,7 @@
           <t>Fechadura 3F modelo Bico Papagaio.</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10787,11 +10643,7 @@
           <t>Fechadura 3F 501, um dispositivo de segurança para portas.</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10883,11 +10735,7 @@
           <t>Fechadura de portão da marca 3F, dispositivo de segurança para portões.</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10931,11 +10779,7 @@
           <t>Fechadura de portão sobrepor Tetra 3F, um dispositivo de segurança para portões.</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11219,11 +11063,7 @@
           <t>Fechadura STAM 1003 ESP INOX, um modelo de fechadura em aço inoxidável.</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11267,11 +11107,7 @@
           <t>Fechadura STAM 1006 para porta de bater/correr, rosca quadrada, acabamento cromado.</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11315,11 +11151,7 @@
           <t>Fechadura STAM 1006 para porta de bater/correr, rosca reduzida, acabamento inox.</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11363,11 +11195,7 @@
           <t>Fechadura STAM 1006S para porta de correr, modelo Classic, adequada para banheiros.</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11411,11 +11239,7 @@
           <t>Fechadura STAM 1008 de bater e correr em inox.</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11459,11 +11283,7 @@
           <t>Fechadura STAM 1201 para porta de aço.</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11507,11 +11327,7 @@
           <t>Fechadura colonial tetra da marca STAM, modelo 1500/06.</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11555,11 +11371,7 @@
           <t>Fechadura colonial da marca STAM, modelo 1501/06.</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11603,11 +11415,7 @@
           <t>Fechadura STAM 1501/09 ESP INOX, um modelo de fechadura em aço inoxidável.</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11699,11 +11507,7 @@
           <t>Fechadura STAM 1601/10 Largo Oxidado. Fechadura de alta qualidade para portas.</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11747,11 +11551,7 @@
           <t>Fechadura STAM 1701/100 3P para portão, com chave tetra.</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11795,11 +11595,7 @@
           <t>Fechadura STAM 1701/100 para portão, com chave tetra.</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11843,11 +11639,7 @@
           <t>Fechadura STAM 1800/17 na cor branca.</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11891,11 +11683,7 @@
           <t>Fechadura STAM 1800/17 na cor Grafite, modelo TETRA.</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11939,11 +11727,7 @@
           <t>Fechadura STAM 1800/21 com acabamento acetinado, modelo TETRA.</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11987,11 +11771,7 @@
           <t>Fechadura STAM 1800/21 na versão escovada, modelo TETRA.</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12035,11 +11815,7 @@
           <t>Fechadura STAM 1800/21 INOX (TETRA), um modelo de fechadura em aço inoxidável.</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12083,11 +11859,7 @@
           <t>Fechadura STAM 1800/21 com acabamento oxidado, modelo Tetra.</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12131,11 +11903,7 @@
           <t>Fechadura STAM 1803/19 ESP INOX, um modelo de fechadura em aço inoxidável.</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12179,11 +11947,7 @@
           <t>Fechadura STAM 201 para porta de aço.</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12227,11 +11991,7 @@
           <t>Fechadura STAM 401/07 ESP INOX, um modelo de fechadura em aço inoxidável.</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12275,11 +12035,7 @@
           <t>Fechadura STAM 501/03-02 ESP INOX, um modelo de fechadura em aço inoxidável.</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12323,11 +12079,7 @@
           <t>Fechadura STAM 502/03-02 na cor branca.</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12371,11 +12123,7 @@
           <t>Fechadura STAM 601/03-02 ESP INOX, um modelo de fechadura em aço inoxidável.</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12419,11 +12167,7 @@
           <t>Fechadura STAM 601/602/03-02 em inox branca.</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12515,11 +12259,7 @@
           <t>Fechadura STAM 603/07 BUZ ESP INOX. Fechadura de alta qualidade em inox.</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12563,11 +12303,7 @@
           <t>Fechadura STAM 603/11 com maçaneta branca, modelo 1/2.</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12611,11 +12347,7 @@
           <t>Fechadura STAM 603/11 com maçaneta de 1/2 polegada em inox.</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12659,11 +12391,7 @@
           <t>Fechadura STAM 701, um dispositivo de segurança para portas.</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12755,11 +12483,7 @@
           <t>Fechadura STAM 803/03-02 ESP INOX, um modelo de fechadura em aço inoxidável.</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12803,11 +12527,7 @@
           <t>Fechadura STAM 803/03-02 na cor grafite.</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12851,11 +12571,7 @@
           <t>Fechadura STAM 803/03-02 na cor inox branca.</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12899,11 +12615,7 @@
           <t>Fechadura STAM 803/03-02 com acabamento oxidado.</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12947,11 +12659,7 @@
           <t>Fechadura colonial da marca STAM, modelo 803/03-04.</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -12995,11 +12703,7 @@
           <t>Fechadura colonial da marca STAM, modelo 813, destinada para uso em quartos.</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13043,11 +12747,7 @@
           <t>Fechadura STAM 813/03 para quarto.</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13086,16 +12786,8 @@
           <t>FECHADURA</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Fechadura STAM 823 para banheiro. Produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13139,11 +12831,7 @@
           <t>Fechadura STAM 901 com design de bico de papagaio.</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13187,11 +12875,7 @@
           <t>Fechadura elétrica STAM modelo CIL 40, que abre para dentro.</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13235,11 +12919,7 @@
           <t>Kit de fechadura colonial tetra da marca STAM, modelo 1500/06.</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13283,11 +12963,7 @@
           <t>Trava interna Salvador 101 sem chave, um dispositivo de segurança para portas.</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13379,11 +13055,7 @@
           <t>Trava lateral Tetra 1001/3 AL na cor vermelha, fabricada pela São Salvador.</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13427,11 +13099,7 @@
           <t>Trava lateral Tetra 1001/4 FF na cor preta, fabricada pela São Salvador.</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -13619,11 +13287,7 @@
           <t>Fecho fio redondo FG 3''. Pequeno dispositivo de fechamento para fios, provavelmente usado em aplicações de organização de cabos.</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14099,11 +13763,7 @@
           <t>Tranqueta caracol completa, dispositivo utilizado para ajustar e fixar estruturas.</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14195,11 +13855,7 @@
           <t>Tranqueta Zinc 86108/2 Aliança, um dispositivo de fixação utilizado em portas e janelas.</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14579,11 +14235,7 @@
           <t>Trinco Tarjeta de 51mm, um dispositivo de fechamento para portas.</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14723,11 +14375,7 @@
           <t>ROD 6X2 ANDAIME C/FREIO PU-ESFERA (4058) é uma roda de andaime com freio e esfera de poliuretano.</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14771,11 +14419,7 @@
           <t>ROD 6X2 ANDAIME C/FREIO PVC, um equipamento de movimentação para andaimes com sistema de freio e revestimento em PVC.</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14963,11 +14607,7 @@
           <t>Rodízio Aliança com haste rosqueada, utilizado em móveis e equipamentos que necessitam de movimentação suave e precisa.</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15011,11 +14651,7 @@
           <t>Rodízio com castanha, produto não especificado.</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15059,11 +14695,7 @@
           <t>Rodízio com castanha dupla, utilizado para facilitar o movimento de móveis e equipamentos.</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15102,16 +14734,8 @@
           <t>RODIZIO</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15347,11 +14971,7 @@
           <t>Rodízio fixo 312 preto Coral C PL 80x105, modelo BP (6240) ATE.</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16691,11 +16311,7 @@
           <t>Rodízio de mesa Aliança N.16, um acessório para facilitar a rotação de mesas em restaurantes e outros estabelecimentos.</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16739,11 +16355,7 @@
           <t>Rodízio de mesa Aliança N.17, um acessório para facilitar a rotação de mesas em restaurantes, bares e outros estabelecimentos.</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16787,11 +16399,7 @@
           <t>Rodízio de mesa Aliança N.20, um acessório para facilitar a rotação de mesas em restaurantes e eventos.</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16835,11 +16443,7 @@
           <t>Rodízio de mesa Aliança N.21, um acessório para facilitar a rotação de pratos e utensílios na mesa.</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17795,11 +17399,7 @@
           <t>Rodízio SGPL 614 BP, um equipamento para movimentação de cargas.</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17843,11 +17443,7 @@
           <t>Rodízio SGPLF 614 BP, um componente para móveis e equipamentos.</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17934,16 +17530,8 @@
           <t>ROLDANA</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. A busca retornou um erro.</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17982,16 +17570,8 @@
           <t>ROLDANA</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. A busca retornou um erro.</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18030,16 +17610,8 @@
           <t>ROLDANA</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18078,16 +17650,8 @@
           <t>ROLDANA</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. A busca retornou um erro.</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18419,11 +17983,7 @@
           <t>ROLDANA RED 1/2 CX FECHADA (2") (020311) é uma roldana de 2 polegadas, com caixa fechada, na cor vermelha.</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18467,11 +18027,7 @@
           <t>ROLDANA RED 1/2 PINO (2") é um componente de fixação, provavelmente utilizado em aplicações de construção ou montagem.</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18563,11 +18119,7 @@
           <t>Roldana Red 5/8 CX Fechada (2.1/2") (030312).</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18851,11 +18403,7 @@
           <t>ROLDANA U 1/2 BG CX FECHADA (2.1/2") (980321). Peça de fixação e roldana para aplicações diversas.</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19187,11 +18735,7 @@
           <t>ROLDANA U 1/2 FIX LATERAL (2") (080385) é um componente de fixação lateral para aplicações que exigem resistência e precisão.</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19235,11 +18779,7 @@
           <t>ROLDANA U 1/2 FIX LATERAL (2.1/2") *(080386) é uma roldana fixa lateral de 2.1/2 polegadas.</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19715,11 +19255,7 @@
           <t>ROLDANA U 3/4 FIX LATERAL (3") P/ MECANICO (010353). Uma roldana fixa lateral de 3 polegadas para uso mecânico.</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19859,11 +19395,7 @@
           <t>ROLDANA U 3/4 PINO (3") (091352) é uma roldana de 3 polegadas com pino, utilizada em diversos equipamentos e aplicações industriais.</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20147,11 +19679,7 @@
           <t>ROLDANA V CX ABERTA (2.1/2") * (010332). Este é um componente mecânico utilizado em sistemas de roldanas.</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20339,11 +19867,7 @@
           <t>ROLDANA V CX FECHADA (2.1/2") (010312) é uma roldana fechada de 2.1/2 polegadas.</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20387,11 +19911,7 @@
           <t>ROLDANA V CX FECHADA (3") (010313) é uma peça de equipamento, possivelmente utilizada em sistemas de içamento ou roldanas.</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20483,11 +20003,7 @@
           <t>ROLDANA V FIX LATERAL (2.1/2") é um componente de fixação lateral, provavelmente utilizado em sistemas de içamento ou suporte.</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20675,11 +20191,7 @@
           <t>ROLDANA V PINO (2.1/2") (011302). Parece ser um componente mecânico, provavelmente usado em equipamentos industriais ou veículos.</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>Não encontradas especificações técnicas no contexto fornecido.</t>
-        </is>
-      </c>
+      <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20771,11 +20283,7 @@
           <t>ROLDANA V PINO (4") * (011305) é um componente mecânico, provavelmente utilizado em sistemas de içamento ou roldanas.</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20867,11 +20375,7 @@
           <t>ROLDANA V PINO de 6 polegadas, código 011307.</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21635,11 +21139,7 @@
           <t>Perfil U de 2 polegadas, produto promocional.</t>
         </is>
       </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21779,11 +21279,7 @@
           <t>Kit de cerâmica Veda Fix Colonial, composto por peças para instalação e vedação de tubulações.</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -22259,11 +21755,7 @@
           <t>Telha de Galvalume com ondulação, com 6 metros de comprimento.</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -23939,11 +23431,7 @@
           <t>Serra Tico-Tico Bi Metal BU 036, uma ferramenta de corte versátil para madeira e metais.</t>
         </is>
       </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -24083,11 +23571,7 @@
           <t>Telha Galvalume de 1,5 metros, oferecida em promoção.</t>
         </is>
       </c>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -24563,11 +24047,7 @@
           <t>Telha Galvalume de 6,5 metros, em promoção.</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G503" t="inlineStr"/>
       <c r="H503" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -24611,11 +24091,7 @@
           <t>Telha Galvalume de 7,0 metros, oferecida em promoção.</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -24659,11 +24135,7 @@
           <t>Telha Galvalume de 7,5 metros, produto em promoção.</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G505" t="inlineStr"/>
       <c r="H505" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -24707,11 +24179,7 @@
           <t>Telha Galvalume de 8,0 metros. Produto em promoção.</t>
         </is>
       </c>
-      <c r="G506" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G506" t="inlineStr"/>
       <c r="H506" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -24755,11 +24223,7 @@
           <t>Telha Galvalume em promoção, um produto resistente e durável para coberturas.</t>
         </is>
       </c>
-      <c r="G507" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -25715,11 +25179,7 @@
           <t>Telha Galvalume Trap para áreas acima de 50 metros quadrados.</t>
         </is>
       </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G527" t="inlineStr"/>
       <c r="H527" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -26483,11 +25943,7 @@
           <t>Disco de corte diamantado para aço da marca Norton.</t>
         </is>
       </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G543" t="inlineStr"/>
       <c r="H543" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -26579,11 +26035,7 @@
           <t>Disco de remoção Strip Disc Norton, utilizado para remoção de materiais e acabamento em superfícies.</t>
         </is>
       </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G545" t="inlineStr"/>
       <c r="H545" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27491,11 +26943,7 @@
           <t>Disco de corte para madeira da marca Ranger, utilizado em ferramentas elétricas para cortes precisos.</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G564" t="inlineStr"/>
       <c r="H564" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27539,11 +26987,7 @@
           <t>Disco de serra circular Widea Ranger, utilizado para cortes precisos em madeira e outros materiais.</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G565" t="inlineStr"/>
       <c r="H565" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27635,11 +27079,7 @@
           <t>Disco diamantado da marca Irwin, modelo 13891, para uso refrigeração liso.</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G567" t="inlineStr"/>
       <c r="H567" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27683,11 +27123,7 @@
           <t>Disco diamantado da marca Irwin, modelo refrigerado segmentado, código 13892. Utilizado para corte de materiais duros como cerâmica e concreto.</t>
         </is>
       </c>
-      <c r="G568" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G568" t="inlineStr"/>
       <c r="H568" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27731,11 +27167,7 @@
           <t>Disco diamantado da marca Irwin, modelo Turbo, para uso refrigeração. Código do produto: 13893.</t>
         </is>
       </c>
-      <c r="G569" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G569" t="inlineStr"/>
       <c r="H569" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27779,11 +27211,7 @@
           <t>Disco diamantado liso Ranger, utilizado para corte de materiais duros como granito, concreto e cerâmica.</t>
         </is>
       </c>
-      <c r="G570" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G570" t="inlineStr"/>
       <c r="H570" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27827,11 +27255,7 @@
           <t>Disco diamantado para porcelanato raiado, ideal para corte preciso e limpo em superfícies cerâmicas.</t>
         </is>
       </c>
-      <c r="G571" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G571" t="inlineStr"/>
       <c r="H571" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27875,11 +27299,7 @@
           <t>Disco diamantado multi corte Ranger, utilizado para cortes precisos em diversos materiais.</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G572" t="inlineStr"/>
       <c r="H572" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27923,11 +27343,7 @@
           <t>Disco diamantado Norton segmentado Classic, utilizado para corte de materiais duros.</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G573" t="inlineStr"/>
       <c r="H573" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -28019,11 +27435,7 @@
           <t>Disco diamantado para corte de porcelanato, proporcionando precisão e durabilidade na aplicação.</t>
         </is>
       </c>
-      <c r="G575" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G575" t="inlineStr"/>
       <c r="H575" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -28067,11 +27479,7 @@
           <t>Disco diamantado segmentado Ranger, utilizado para corte de materiais duros como granito, concreto e cerâmica.</t>
         </is>
       </c>
-      <c r="G576" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G576" t="inlineStr"/>
       <c r="H576" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -28115,11 +27523,7 @@
           <t>Disco diamantado Turbo Ranger, utilizado para corte de materiais duros como concreto e granito.</t>
         </is>
       </c>
-      <c r="G577" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G577" t="inlineStr"/>
       <c r="H577" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -28691,11 +28095,7 @@
           <t>Trena Bono 10, um dispositivo de medição portátil para uso em diversas atividades.</t>
         </is>
       </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G589" t="inlineStr"/>
       <c r="H589" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -28787,11 +28187,7 @@
           <t>Brosse quadrada de nylon, modelo Max, para limpeza geral.</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G591" t="inlineStr"/>
       <c r="H591" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -28835,11 +28231,7 @@
           <t>Broxa redonda feita de nylon com cabo de PVC.</t>
         </is>
       </c>
-      <c r="G592" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G592" t="inlineStr"/>
       <c r="H592" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -29214,16 +28606,8 @@
           <t>PINCEIS E ACESSORIOS</t>
         </is>
       </c>
-      <c r="F600" t="inlineStr">
-        <is>
-          <t>Trincha de 1 polegada. Produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G600" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
       <c r="H600" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -29267,11 +28651,7 @@
           <t>Trincha 1.1/2, um utensílio de corte utilizado em cozinhas profissionais e residenciais.</t>
         </is>
       </c>
-      <c r="G601" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G601" t="inlineStr"/>
       <c r="H601" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -29358,16 +28738,8 @@
           <t>PINCEIS E ACESSORIOS</t>
         </is>
       </c>
-      <c r="F603" t="inlineStr">
-        <is>
-          <t>Trincha de 2 polegadas. Produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G603" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr"/>
       <c r="H603" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30419,11 +29791,7 @@
           <t>Rebite em cartela contendo 100 peças, modelo 308 (429).</t>
         </is>
       </c>
-      <c r="G625" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G625" t="inlineStr"/>
       <c r="H625" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30659,11 +30027,7 @@
           <t>Rebite em cartela contendo 100 peças, modelo 410 (540).</t>
         </is>
       </c>
-      <c r="G630" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G630" t="inlineStr"/>
       <c r="H630" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30755,11 +30119,7 @@
           <t>Rebite POP 306 (423) KG, um rebite utilizado para fixação em aplicações industriais.</t>
         </is>
       </c>
-      <c r="G632" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G632" t="inlineStr"/>
       <c r="H632" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30803,11 +30163,7 @@
           <t>Rebite POP 308 (429) KG. Um tipo de rebite utilizado para fixação em diversos materiais.</t>
         </is>
       </c>
-      <c r="G633" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G633" t="inlineStr"/>
       <c r="H633" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31139,11 +30495,7 @@
           <t>Rebite POP 416 (565) KG. Este rebite é utilizado para fixação em materiais leves e metálicos.</t>
         </is>
       </c>
-      <c r="G640" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G640" t="inlineStr"/>
       <c r="H640" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31187,11 +30539,7 @@
           <t>Rebite POP 422 (585) KG, um rebite utilizado para fixação em aplicações industriais.</t>
         </is>
       </c>
-      <c r="G641" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G641" t="inlineStr"/>
       <c r="H641" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31235,11 +30583,7 @@
           <t>Rebite POP 425 (5100) KG, um rebite utilizado para fixação em aplicações industriais e de construção.</t>
         </is>
       </c>
-      <c r="G642" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G642" t="inlineStr"/>
       <c r="H642" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31379,11 +30723,7 @@
           <t>Rebite Pop 516 (665) KG, um rebite utilizado para fixação em aplicações industriais.</t>
         </is>
       </c>
-      <c r="G645" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G645" t="inlineStr"/>
       <c r="H645" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31427,11 +30767,7 @@
           <t>Rebite POP 519 (673) KG, um rebite utilizado para fixação em aplicações industriais.</t>
         </is>
       </c>
-      <c r="G646" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G646" t="inlineStr"/>
       <c r="H646" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31475,11 +30811,7 @@
           <t>Rebite POP 522 (685) KG, um rebite utilizado para fixação em aplicações diversas.</t>
         </is>
       </c>
-      <c r="G647" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G647" t="inlineStr"/>
       <c r="H647" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31523,11 +30855,7 @@
           <t>Rebite POP 525 (6100) KG, um rebite utilizado para fixação em aplicações industriais.</t>
         </is>
       </c>
-      <c r="G648" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G648" t="inlineStr"/>
       <c r="H648" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31571,11 +30899,7 @@
           <t>Rebite POP 535 (6119) KG, um rebite utilizado para fixação em aplicações industriais.</t>
         </is>
       </c>
-      <c r="G649" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G649" t="inlineStr"/>
       <c r="H649" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31619,11 +30943,7 @@
           <t>Rebite POP 619 (873) KG, um rebite utilizado em aplicações industriais para fixação de peças.</t>
         </is>
       </c>
-      <c r="G650" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G650" t="inlineStr"/>
       <c r="H650" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31667,11 +30987,7 @@
           <t>Rebite POP 630 (8119) KG, um rebite utilizado para fixação em aplicações industriais.</t>
         </is>
       </c>
-      <c r="G651" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G651" t="inlineStr"/>
       <c r="H651" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -33635,11 +32951,7 @@
           <t>Barra chata de dimensões 1 x 1/4, utilizada em construções metálicas e montagens industriais.</t>
         </is>
       </c>
-      <c r="G692" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G692" t="inlineStr"/>
       <c r="H692" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34451,11 +33763,7 @@
           <t>Barra chata de 1/2 polegada utilizada por serralheiros para diversos tipos de trabalhos.</t>
         </is>
       </c>
-      <c r="G709" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G709" t="inlineStr"/>
       <c r="H709" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34643,11 +33951,7 @@
           <t>Barra chata de dimensões 2 x 1/4, utilizada em construções e montagens metálicas.</t>
         </is>
       </c>
-      <c r="G713" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G713" t="inlineStr"/>
       <c r="H713" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35027,11 +34331,7 @@
           <t>Barra chata de dimensões 3 x 1/2, utilizada em diversas aplicações de construção e metalurgia.</t>
         </is>
       </c>
-      <c r="G721" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G721" t="inlineStr"/>
       <c r="H721" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36131,11 +35431,7 @@
           <t>Barra redonda de material não especificado, sem detalhes adicionais disponíveis.</t>
         </is>
       </c>
-      <c r="G744" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G744" t="inlineStr"/>
       <c r="H744" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36803,11 +36099,7 @@
           <t>Chapa de alumínio com 1,0 metro de comprimento.</t>
         </is>
       </c>
-      <c r="G758" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G758" t="inlineStr"/>
       <c r="H758" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36851,11 +36143,7 @@
           <t>Chapa de alumínio com 20 cm de comprimento.</t>
         </is>
       </c>
-      <c r="G759" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G759" t="inlineStr"/>
       <c r="H759" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36899,11 +36187,7 @@
           <t>Chapa de alumínio com 30 cm de comprimento.</t>
         </is>
       </c>
-      <c r="G760" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G760" t="inlineStr"/>
       <c r="H760" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36947,11 +36231,7 @@
           <t>Chapa de alumínio com 40 cm de comprimento.</t>
         </is>
       </c>
-      <c r="G761" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G761" t="inlineStr"/>
       <c r="H761" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36995,11 +36275,7 @@
           <t>Chapa de alumínio com 50 cm de comprimento.</t>
         </is>
       </c>
-      <c r="G762" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -37043,11 +36319,7 @@
           <t>Chapa de alumínio com 60 cm de comprimento.</t>
         </is>
       </c>
-      <c r="G763" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G763" t="inlineStr"/>
       <c r="H763" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -37091,11 +36363,7 @@
           <t>Chapa de alumínio com 80 cm de comprimento.</t>
         </is>
       </c>
-      <c r="G764" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42035,11 +41303,7 @@
           <t>Retalho de chapa galvanizada, material resistente e durável para diversos usos.</t>
         </is>
       </c>
-      <c r="G867" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G867" t="inlineStr"/>
       <c r="H867" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43043,11 +42307,7 @@
           <t>Chapa preta de 18 polegadas, com dimensões de 2 x 1.</t>
         </is>
       </c>
-      <c r="G888" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G888" t="inlineStr"/>
       <c r="H888" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43523,11 +42783,7 @@
           <t>Chapa preta de 22 polegadas, com 2 unidades por pacote.</t>
         </is>
       </c>
-      <c r="G898" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G898" t="inlineStr"/>
       <c r="H898" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43667,11 +42923,7 @@
           <t>Chapa preta de 24 polegadas, com dimensões 2 x 1.</t>
         </is>
       </c>
-      <c r="G901" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G901" t="inlineStr"/>
       <c r="H901" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43715,11 +42967,7 @@
           <t>Chapa preta de 24 polegadas, com 2 x 1 emp2.</t>
         </is>
       </c>
-      <c r="G902" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G902" t="inlineStr"/>
       <c r="H902" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44339,11 +43587,7 @@
           <t>Chapa preta FF 16 = 2 X 1. Parece ser um produto relacionado a chapas ou placas, mas sem mais detalhes disponíveis.</t>
         </is>
       </c>
-      <c r="G915" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G915" t="inlineStr"/>
       <c r="H915" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44430,16 +43674,8 @@
           <t>PRETA LISA</t>
         </is>
       </c>
-      <c r="F917" t="inlineStr">
-        <is>
-          <t>Chapa preta FF 16 = 3 X 1. Produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G917" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="inlineStr"/>
       <c r="H917" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44483,11 +43719,7 @@
           <t>Chapa preta FF 16 = 3 X 1 EMP2, um produto de metal para construção ou reparo.</t>
         </is>
       </c>
-      <c r="G918" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G918" t="inlineStr"/>
       <c r="H918" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44627,11 +43859,7 @@
           <t>Chapa preta FQ 1/2 = 2 X 1, um produto de metal para construção e indústria.</t>
         </is>
       </c>
-      <c r="G921" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G921" t="inlineStr"/>
       <c r="H921" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44675,11 +43903,7 @@
           <t>Chapa preta FQ 1/4 = 2 X 1, um produto de metal para construção e reparos.</t>
         </is>
       </c>
-      <c r="G922" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G922" t="inlineStr"/>
       <c r="H922" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44723,11 +43947,7 @@
           <t>Chapa preta FQ 1/4 = 2 X 1 EMP 2. Produto utilizado em aplicações industriais e construções metálicas.</t>
         </is>
       </c>
-      <c r="G923" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G923" t="inlineStr"/>
       <c r="H923" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44819,11 +44039,7 @@
           <t>Chapa preta FQ 1/4 = 3 X 1, um produto de metal para construção e indústria.</t>
         </is>
       </c>
-      <c r="G925" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G925" t="inlineStr"/>
       <c r="H925" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46499,11 +45715,7 @@
           <t>Perfil TEE 3/4 utilizado em obras e construções metálicas.</t>
         </is>
       </c>
-      <c r="G960" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G960" t="inlineStr"/>
       <c r="H960" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46787,11 +45999,7 @@
           <t>O ESC FIBRA EXTENSIVA ROBUSTA 18 (9927) é um produto cujas informações não foram encontradas.</t>
         </is>
       </c>
-      <c r="G966" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G966" t="inlineStr"/>
       <c r="H966" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46835,11 +46043,7 @@
           <t>Extensão de fibra óptica robusta, modelo ESC FIBRA EXTENSIVA ROBUSTA 20 (9928).</t>
         </is>
       </c>
-      <c r="G967" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G967" t="inlineStr"/>
       <c r="H967" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46883,11 +46087,7 @@
           <t>O ESC FIBRA EXTENSIVA ROBUSTA 24 (9930) é um produto relacionado a fibra extensiva robusta, com 24 unidades.</t>
         </is>
       </c>
-      <c r="G968" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G968" t="inlineStr"/>
       <c r="H968" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46931,11 +46131,7 @@
           <t>O ESC FIBRA EXTENSIVA ROBUSTA 28 (9932) é um produto cujas informações não foram encontradas na busca web.</t>
         </is>
       </c>
-      <c r="G969" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G969" t="inlineStr"/>
       <c r="H969" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46979,11 +46175,7 @@
           <t>O ESC FIBRA EXTENSIVA ROBUSTA 30 (9933) é um produto de fibra extensiva robusta, indicado para aplicações que exigem alta resistência e durabilidade.</t>
         </is>
       </c>
-      <c r="G970" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G970" t="inlineStr"/>
       <c r="H970" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47027,11 +46219,7 @@
           <t>O ESC FIBRA EXTENSIVA ROBUSTA 36 (9936) é um produto relacionado a fibra extensiva robusta, com 36 unidades.</t>
         </is>
       </c>
-      <c r="G971" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G971" t="inlineStr"/>
       <c r="H971" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47075,11 +46263,7 @@
           <t>Escada Art 13 em 1 de alumínio, um modelo versátil com múltiplas configurações para diferentes usos.</t>
         </is>
       </c>
-      <c r="G972" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G972" t="inlineStr"/>
       <c r="H972" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47123,11 +46307,7 @@
           <t>Escada de alumínio ART 13 em 1, modelo 5x4, com múltiplas configurações de uso.</t>
         </is>
       </c>
-      <c r="G973" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G973" t="inlineStr"/>
       <c r="H973" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47171,11 +46351,7 @@
           <t>Escada doméstica de alumínio com 5 degraus da marca BFT, modelo 0064.</t>
         </is>
       </c>
-      <c r="G974" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G974" t="inlineStr"/>
       <c r="H974" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47219,11 +46395,7 @@
           <t>Escada doméstica de alumínio com 7 degraus da marca BFT, modelo 0066.</t>
         </is>
       </c>
-      <c r="G975" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G975" t="inlineStr"/>
       <c r="H975" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47267,11 +46439,7 @@
           <t>Escada doméstica de alumínio da marca BFT, modelo 0068, com 9 degraus.</t>
         </is>
       </c>
-      <c r="G976" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G976" t="inlineStr"/>
       <c r="H976" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47315,11 +46483,7 @@
           <t>Escada doméstica de alumínio BFG Pro 6Deg, modelo 0026.</t>
         </is>
       </c>
-      <c r="G977" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G977" t="inlineStr"/>
       <c r="H977" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47363,11 +46527,7 @@
           <t>Escada doméstica de alumínio BFG Pro 7Deg, modelo 0027.</t>
         </is>
       </c>
-      <c r="G978" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G978" t="inlineStr"/>
       <c r="H978" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47411,11 +46571,7 @@
           <t>Escada extensiva de alumínio com 12 degraus, modelo 00621.</t>
         </is>
       </c>
-      <c r="G979" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G979" t="inlineStr"/>
       <c r="H979" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47507,11 +46663,7 @@
           <t>Escada extensiva de alumínio com 8 degraus, modelo 00617.</t>
         </is>
       </c>
-      <c r="G981" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G981" t="inlineStr"/>
       <c r="H981" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47555,11 +46707,7 @@
           <t>Escada extensiva tripla de alumínio com 9 degraus, modelo 00709.</t>
         </is>
       </c>
-      <c r="G982" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G982" t="inlineStr"/>
       <c r="H982" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47747,11 +46895,7 @@
           <t>Escada de fibra extensível Prática 13DE, modelo 9913. Este produto saiu de linha.</t>
         </is>
       </c>
-      <c r="G986" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G986" t="inlineStr"/>
       <c r="H986" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47795,11 +46939,7 @@
           <t>Escada de fibra extensível prática, modelo 19DE 9919.</t>
         </is>
       </c>
-      <c r="G987" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G987" t="inlineStr"/>
       <c r="H987" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47843,11 +46983,7 @@
           <t>Escada de fibra tesoura Prática 8 degraus da marca BTF, modelo 9903.</t>
         </is>
       </c>
-      <c r="G988" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G988" t="inlineStr"/>
       <c r="H988" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47891,11 +47027,7 @@
           <t>Escada paralela de alumínio, modelo 10DE - 0608.</t>
         </is>
       </c>
-      <c r="G989" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G989" t="inlineStr"/>
       <c r="H989" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47939,11 +47071,7 @@
           <t>Escada paralela de alumínio, modelo 12DE - 0610.</t>
         </is>
       </c>
-      <c r="G990" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G990" t="inlineStr"/>
       <c r="H990" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47987,11 +47115,7 @@
           <t>Escada paralela de alumínio com 14 degraus, modelo 0612.</t>
         </is>
       </c>
-      <c r="G991" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G991" t="inlineStr"/>
       <c r="H991" t="inlineStr">
         <is>
           <t>Não encontrado</t>
